--- a/TALENTO_EAFIT_Carga_Masiva.xlsx
+++ b/TALENTO_EAFIT_Carga_Masiva.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,20 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -86,8 +98,13 @@
         <fgColor rgb="0016a34a"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000057a8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -109,11 +126,17 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -138,6 +161,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA52"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -534,6 +566,9 @@
     <col width="45" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
     <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -679,6 +714,21 @@
           <t>Fecha Firma (DD/MM/AAAA)</t>
         </is>
       </c>
+      <c r="AB2" s="9" t="inlineStr">
+        <is>
+          <t>Email Organizacion</t>
+        </is>
+      </c>
+      <c r="AC2" s="9" t="inlineStr">
+        <is>
+          <t>Email Estudiante</t>
+        </is>
+      </c>
+      <c r="AD2" s="9" t="inlineStr">
+        <is>
+          <t>Email EAFIT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -808,6 +858,21 @@
           <t>01/02/2025</t>
         </is>
       </c>
+      <c r="AB3" s="10" t="inlineStr">
+        <is>
+          <t>firma@empresa.com</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="inlineStr">
+        <is>
+          <t>estudiante@eafit.edu.co</t>
+        </is>
+      </c>
+      <c r="AD3" s="10" t="inlineStr">
+        <is>
+          <t>asesor@eafit.edu.co</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -937,6 +1002,9 @@
           <t>05/06/2025</t>
         </is>
       </c>
+      <c r="AB4" s="11" t="inlineStr"/>
+      <c r="AC4" s="11" t="inlineStr"/>
+      <c r="AD4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1074,6 +1142,9 @@
           <t>15/07/2025</t>
         </is>
       </c>
+      <c r="AB5" s="11" t="inlineStr"/>
+      <c r="AC5" s="11" t="inlineStr"/>
+      <c r="AD5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
